--- a/input/reg_health.xlsx
+++ b/input/reg_health.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{B2B54236-0D77-4045-AD5F-6E5E09566883}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{6A2A5CE9-A86C-4512-B0A5-5FCEB54C43D9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-83" yWindow="0" windowWidth="14566" windowHeight="17363" tabRatio="675" activeTab="3" xr2:uid="{8F8EB3C6-ADA8-4D50-A668-C6931E9C8858}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" tabRatio="675" activeTab="1" xr2:uid="{8F8EB3C6-ADA8-4D50-A668-C6931E9C8858}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="10" r:id="rId1"/>
@@ -37,7 +37,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="129">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="256" uniqueCount="128">
   <si>
     <t>REGRESSOR</t>
   </si>
@@ -388,9 +388,6 @@
   </si>
   <si>
     <t>Dhe_L1_Fair</t>
-  </si>
-  <si>
-    <t>Dhe_L1_good</t>
   </si>
   <si>
     <t>Dhe_L1_VeryGood</t>
@@ -900,66 +897,67 @@
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="25.86328125" customWidth="1"/>
+    <col min="10" max="10" width="12.796875" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A1" s="6" t="s">
+      <c r="A1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="6" t="s">
+      <c r="B1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" t="s">
         <v>89</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" t="s">
         <v>90</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="7" t="s">
+      <c r="F1" t="s">
         <v>91</v>
       </c>
-      <c r="G1" s="7" t="s">
+      <c r="G1" t="s">
         <v>92</v>
       </c>
-      <c r="H1" s="7" t="s">
+      <c r="H1" t="s">
         <v>93</v>
       </c>
-      <c r="I1" s="7" t="s">
+      <c r="I1" t="s">
         <v>94</v>
       </c>
-      <c r="J1" s="7" t="s">
+      <c r="J1" t="s">
         <v>115</v>
       </c>
-      <c r="K1" s="7" t="s">
+      <c r="K1" t="s">
         <v>42</v>
       </c>
-      <c r="L1" s="7" t="s">
+      <c r="L1" t="s">
         <v>116</v>
       </c>
-      <c r="M1" s="7" t="s">
+      <c r="M1" t="s">
         <v>48</v>
       </c>
-      <c r="N1" s="7" t="s">
+      <c r="N1" t="s">
+        <v>118</v>
+      </c>
+      <c r="O1" t="s">
+        <v>54</v>
+      </c>
+      <c r="P1" t="s">
         <v>117</v>
       </c>
-      <c r="O1" s="7" t="s">
-        <v>54</v>
-      </c>
-      <c r="P1" s="7" t="s">
-        <v>118</v>
-      </c>
-      <c r="Q1" s="7" t="s">
+      <c r="Q1" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="2" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A2" s="6" t="s">
+      <c r="A2" t="s">
         <v>89</v>
       </c>
-      <c r="B2" s="6">
+      <c r="B2">
         <v>5.761542280896978E-2</v>
       </c>
       <c r="C2">
@@ -1009,10 +1007,10 @@
       </c>
     </row>
     <row r="3" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A3" s="7" t="s">
+      <c r="A3" t="s">
         <v>90</v>
       </c>
-      <c r="B3" s="6">
+      <c r="B3">
         <v>0.46609329898246343</v>
       </c>
       <c r="C3">
@@ -1062,10 +1060,10 @@
       </c>
     </row>
     <row r="4" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A4" s="6" t="s">
+      <c r="A4" t="s">
         <v>114</v>
       </c>
-      <c r="B4" s="6">
+      <c r="B4">
         <v>-9.2154242387127352E-3</v>
       </c>
       <c r="C4">
@@ -1115,10 +1113,10 @@
       </c>
     </row>
     <row r="5" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A5" s="6" t="s">
+      <c r="A5" t="s">
         <v>91</v>
       </c>
-      <c r="B5" s="6">
+      <c r="B5">
         <v>0.10455071193044765</v>
       </c>
       <c r="C5">
@@ -1168,10 +1166,10 @@
       </c>
     </row>
     <row r="6" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A6" s="6" t="s">
+      <c r="A6" t="s">
         <v>92</v>
       </c>
-      <c r="B6" s="6">
+      <c r="B6">
         <v>0.1109244106331525</v>
       </c>
       <c r="C6">
@@ -1221,10 +1219,10 @@
       </c>
     </row>
     <row r="7" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A7" s="6" t="s">
+      <c r="A7" t="s">
         <v>93</v>
       </c>
-      <c r="B7" s="6">
+      <c r="B7">
         <v>-4.0521315647638202E-2</v>
       </c>
       <c r="C7">
@@ -1274,10 +1272,10 @@
       </c>
     </row>
     <row r="8" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A8" s="6" t="s">
+      <c r="A8" t="s">
         <v>94</v>
       </c>
-      <c r="B8" s="6">
+      <c r="B8">
         <v>7.0313429167784651E-3</v>
       </c>
       <c r="C8">
@@ -1327,10 +1325,10 @@
       </c>
     </row>
     <row r="9" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A9" s="6" t="s">
+      <c r="A9" t="s">
         <v>115</v>
       </c>
-      <c r="B9" s="6">
+      <c r="B9">
         <v>2.0918379312580062</v>
       </c>
       <c r="C9">
@@ -1380,10 +1378,10 @@
       </c>
     </row>
     <row r="10" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A10" s="6" t="s">
+      <c r="A10" t="s">
         <v>42</v>
       </c>
-      <c r="B10" s="6">
+      <c r="B10">
         <v>-7.6502354247969118</v>
       </c>
       <c r="C10">
@@ -1433,10 +1431,10 @@
       </c>
     </row>
     <row r="11" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A11" s="6" t="s">
+      <c r="A11" t="s">
         <v>116</v>
       </c>
-      <c r="B11" s="6">
+      <c r="B11">
         <v>1.8902973699204106</v>
       </c>
       <c r="C11">
@@ -1486,10 +1484,10 @@
       </c>
     </row>
     <row r="12" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A12" s="6" t="s">
+      <c r="A12" t="s">
         <v>48</v>
       </c>
-      <c r="B12" s="6">
+      <c r="B12">
         <v>-9.1130684735938949</v>
       </c>
       <c r="C12">
@@ -1539,10 +1537,10 @@
       </c>
     </row>
     <row r="13" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A13" s="6" t="s">
-        <v>119</v>
-      </c>
-      <c r="B13" s="6">
+      <c r="A13" t="s">
+        <v>118</v>
+      </c>
+      <c r="B13">
         <v>1.9752988519943409</v>
       </c>
       <c r="C13">
@@ -1592,10 +1590,10 @@
       </c>
     </row>
     <row r="14" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A14" s="6" t="s">
+      <c r="A14" t="s">
         <v>54</v>
       </c>
-      <c r="B14" s="6">
+      <c r="B14">
         <v>-11.314890490027757</v>
       </c>
       <c r="C14">
@@ -1645,10 +1643,10 @@
       </c>
     </row>
     <row r="15" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A15" s="6" t="s">
-        <v>118</v>
-      </c>
-      <c r="B15" s="6">
+      <c r="A15" t="s">
+        <v>117</v>
+      </c>
+      <c r="B15">
         <v>1.6318661220464847</v>
       </c>
       <c r="C15">
@@ -1698,10 +1696,10 @@
       </c>
     </row>
     <row r="16" spans="1:17" x14ac:dyDescent="0.45">
-      <c r="A16" s="6" t="s">
+      <c r="A16" t="s">
         <v>99</v>
       </c>
-      <c r="B16" s="6">
+      <c r="B16">
         <v>-13.04369524597343</v>
       </c>
       <c r="C16">
@@ -1778,7 +1776,7 @@
         <v>96</v>
       </c>
       <c r="E1" s="7" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="F1" s="7" t="s">
         <v>97</v>
@@ -1787,10 +1785,10 @@
         <v>92</v>
       </c>
       <c r="H1" s="7" t="s">
+        <v>120</v>
+      </c>
+      <c r="I1" s="7" t="s">
         <v>121</v>
-      </c>
-      <c r="I1" s="7" t="s">
-        <v>122</v>
       </c>
       <c r="J1" s="6" t="s">
         <v>37</v>
@@ -1829,7 +1827,7 @@
         <v>63</v>
       </c>
       <c r="V1" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="W1" s="6" t="s">
         <v>64</v>
@@ -1880,7 +1878,7 @@
         <v>73</v>
       </c>
       <c r="AM1" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="AN1" s="6" t="s">
         <v>74</v>
@@ -1931,7 +1929,7 @@
         <v>83</v>
       </c>
       <c r="BD1" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="BE1" s="6" t="s">
         <v>84</v>
@@ -1982,7 +1980,7 @@
         <v>110</v>
       </c>
       <c r="BU1" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="BV1" s="6" t="s">
         <v>111</v>
@@ -2465,7 +2463,7 @@
     </row>
     <row r="4" spans="1:77" x14ac:dyDescent="0.45">
       <c r="A4" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B4" s="6">
         <v>5.8147364986608713E-3</v>
@@ -3164,7 +3162,7 @@
     </row>
     <row r="7" spans="1:77" x14ac:dyDescent="0.45">
       <c r="A7" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B7" s="6">
         <v>0.14753749597830657</v>
@@ -3397,7 +3395,7 @@
     </row>
     <row r="8" spans="1:77" x14ac:dyDescent="0.45">
       <c r="A8" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B8" s="6">
         <v>9.1209090803300016E-2</v>
@@ -6426,7 +6424,7 @@
     </row>
     <row r="21" spans="1:77" x14ac:dyDescent="0.45">
       <c r="A21" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="B21" s="6">
         <v>0.33563857687652476</v>
@@ -10387,7 +10385,7 @@
     </row>
     <row r="38" spans="1:77" x14ac:dyDescent="0.45">
       <c r="A38" s="6" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
       <c r="B38" s="6">
         <v>0.18615262052516574</v>
@@ -14348,7 +14346,7 @@
     </row>
     <row r="55" spans="1:77" x14ac:dyDescent="0.45">
       <c r="A55" s="6" t="s">
-        <v>125</v>
+        <v>124</v>
       </c>
       <c r="B55" s="6">
         <v>0.14837160944815669</v>
@@ -18309,7 +18307,7 @@
     </row>
     <row r="72" spans="1:77" x14ac:dyDescent="0.45">
       <c r="A72" s="6" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B72" s="6">
         <v>3.5121458243949466E-2</v>
@@ -19566,10 +19564,10 @@
         <v>16</v>
       </c>
       <c r="AA1" t="s">
+        <v>126</v>
+      </c>
+      <c r="AB1" t="s">
         <v>127</v>
-      </c>
-      <c r="AB1" t="s">
-        <v>128</v>
       </c>
       <c r="AC1" t="s">
         <v>2</v>
@@ -21713,7 +21711,7 @@
     </row>
     <row r="26" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A26" s="6" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B26" s="6">
         <v>0.15977283572343173</v>
@@ -21802,7 +21800,7 @@
     </row>
     <row r="27" spans="1:29" x14ac:dyDescent="0.45">
       <c r="A27" s="6" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B27" s="6">
         <v>0.34635572624410849</v>

--- a/input/reg_health.xlsx
+++ b/input/reg_health.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Patryk\git\SimPaths_HU\input\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55926450-E450-44A0-A6B0-D9EB3BAC0BF9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A10C7FC3-850A-4B74-A282-BE431BD80D65}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-98" yWindow="-98" windowWidth="28996" windowHeight="17475" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Info" sheetId="1" r:id="rId1"/>
@@ -412,9 +412,6 @@
     <t>Ydses_c5_Q5_L1_Good</t>
   </si>
   <si>
-    <t>Dhhtp_c4_SingleNoChildren_L_Good</t>
-  </si>
-  <si>
     <t>Dhhtp_c4_SingleChildren_L1_Good</t>
   </si>
   <si>
@@ -471,20 +468,18 @@
   <si>
     <t>ITI</t>
   </si>
+  <si>
+    <t>Dhhtp_c4_SingleNoChildren_L1_Good</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="3" x14ac:knownFonts="1">
+  <fonts count="2" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <name val="Calibri"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <name val="Calibri"/>
-      <family val="2"/>
     </font>
     <font>
       <b/>
@@ -520,11 +515,9 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="2" fontId="1" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -871,10 +864,10 @@
       </c>
     </row>
     <row r="4" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="1" t="s">
         <v>0</v>
       </c>
     </row>
@@ -923,7 +916,7 @@
       </c>
     </row>
     <row r="14" spans="1:2" x14ac:dyDescent="0.45">
-      <c r="A14" s="3" t="s">
+      <c r="A14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="B14" t="s">
@@ -937,13 +930,13 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8C6C6274-FA8D-9C40-9638-663BD25ED896}">
-  <dimension ref="A1:AA26"/>
+  <dimension ref="A1:Y24"/>
   <sheetFormatPr defaultColWidth="8.86328125" defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="25.86328125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A1" t="s">
         <v>10</v>
       </c>
@@ -1019,10 +1012,8 @@
       <c r="Y1" t="s">
         <v>69</v>
       </c>
-      <c r="Z1" s="1"/>
-      <c r="AA1" s="1"/>
     </row>
-    <row r="2" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A2" t="s">
         <v>102</v>
       </c>
@@ -1099,7 +1090,7 @@
         <v>-0.21551274595847308</v>
       </c>
     </row>
-    <row r="3" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A3" t="s">
         <v>103</v>
       </c>
@@ -1176,7 +1167,7 @@
         <v>-2.0523962341023813E-2</v>
       </c>
     </row>
-    <row r="4" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
         <v>104</v>
       </c>
@@ -1253,7 +1244,7 @@
         <v>-8.883469237265006E-3</v>
       </c>
     </row>
-    <row r="5" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A5" t="s">
         <v>105</v>
       </c>
@@ -1330,7 +1321,7 @@
         <v>-1.6954728854143584E-2</v>
       </c>
     </row>
-    <row r="6" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
         <v>106</v>
       </c>
@@ -1407,7 +1398,7 @@
         <v>9.064406846950499E-4</v>
       </c>
     </row>
-    <row r="7" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A7" t="s">
         <v>107</v>
       </c>
@@ -1484,7 +1475,7 @@
         <v>-1.6946028339353231E-3</v>
       </c>
     </row>
-    <row r="8" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
         <v>70</v>
       </c>
@@ -1561,7 +1552,7 @@
         <v>-4.7905716394571244E-4</v>
       </c>
     </row>
-    <row r="9" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A9" t="s">
         <v>27</v>
       </c>
@@ -1638,7 +1629,7 @@
         <v>2.5164319149042692E-2</v>
       </c>
     </row>
-    <row r="10" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
         <v>29</v>
       </c>
@@ -1715,7 +1706,7 @@
         <v>5.0006551929054144E-3</v>
       </c>
     </row>
-    <row r="11" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A11" t="s">
         <v>71</v>
       </c>
@@ -1792,7 +1783,7 @@
         <v>1.1335334666175836E-2</v>
       </c>
     </row>
-    <row r="12" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A12" t="s">
         <v>37</v>
       </c>
@@ -1869,7 +1860,7 @@
         <v>2.2877864861514214</v>
       </c>
     </row>
-    <row r="13" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A13" t="s">
         <v>38</v>
       </c>
@@ -1946,7 +1937,7 @@
         <v>-1.5880011191553682E-3</v>
       </c>
     </row>
-    <row r="14" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A14" t="s">
         <v>40</v>
       </c>
@@ -2023,7 +2014,7 @@
         <v>4.9183625274909822E-3</v>
       </c>
     </row>
-    <row r="15" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A15" t="s">
         <v>72</v>
       </c>
@@ -2100,7 +2091,7 @@
         <v>3.1947240520238597E-5</v>
       </c>
     </row>
-    <row r="16" spans="1:27" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:25" x14ac:dyDescent="0.45">
       <c r="A16" t="s">
         <v>48</v>
       </c>
@@ -2792,14 +2783,6 @@
       <c r="Y24">
         <v>2.4091828261571853</v>
       </c>
-    </row>
-    <row r="25" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A25" s="2"/>
-      <c r="B25" s="2"/>
-    </row>
-    <row r="26" spans="1:25" x14ac:dyDescent="0.45">
-      <c r="A26" s="2"/>
-      <c r="B26" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -3008,28 +2991,28 @@
         <v>87</v>
       </c>
       <c r="BM1" t="s">
+        <v>148</v>
+      </c>
+      <c r="BN1" t="s">
         <v>129</v>
       </c>
-      <c r="BN1" t="s">
+      <c r="BO1" t="s">
         <v>130</v>
       </c>
-      <c r="BO1" t="s">
+      <c r="BP1" t="s">
         <v>131</v>
       </c>
-      <c r="BP1" t="s">
+      <c r="BQ1" t="s">
         <v>132</v>
       </c>
-      <c r="BQ1" t="s">
+      <c r="BR1" t="s">
         <v>133</v>
-      </c>
-      <c r="BR1" t="s">
-        <v>134</v>
       </c>
       <c r="BS1" t="s">
         <v>57</v>
       </c>
       <c r="BT1" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="BU1" t="s">
         <v>58</v>
@@ -3044,7 +3027,7 @@
         <v>61</v>
       </c>
       <c r="BY1" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="BZ1" t="s">
         <v>99</v>
@@ -3056,10 +3039,10 @@
         <v>62</v>
       </c>
       <c r="CC1" t="s">
+        <v>136</v>
+      </c>
+      <c r="CD1" t="s">
         <v>137</v>
-      </c>
-      <c r="CD1" t="s">
-        <v>138</v>
       </c>
       <c r="CE1" t="s">
         <v>63</v>
@@ -3080,25 +3063,25 @@
         <v>67</v>
       </c>
       <c r="CK1" t="s">
+        <v>138</v>
+      </c>
+      <c r="CL1" t="s">
         <v>139</v>
       </c>
-      <c r="CL1" t="s">
+      <c r="CM1" t="s">
         <v>140</v>
       </c>
-      <c r="CM1" t="s">
+      <c r="CN1" t="s">
         <v>141</v>
       </c>
-      <c r="CN1" t="s">
+      <c r="CO1" t="s">
         <v>142</v>
-      </c>
-      <c r="CO1" t="s">
-        <v>143</v>
       </c>
       <c r="CP1" t="s">
         <v>68</v>
       </c>
       <c r="CQ1" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="CR1" t="s">
         <v>69</v>
@@ -21086,7 +21069,7 @@
     </row>
     <row r="64" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A64" t="s">
-        <v>129</v>
+        <v>148</v>
       </c>
       <c r="B64">
         <v>-0.16800628690702651</v>
@@ -21376,7 +21359,7 @@
     </row>
     <row r="65" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A65" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B65">
         <v>-0.23418639199229077</v>
@@ -21666,7 +21649,7 @@
     </row>
     <row r="66" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A66" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B66">
         <v>-0.13873624306491344</v>
@@ -21956,7 +21939,7 @@
     </row>
     <row r="67" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A67" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B67">
         <v>-0.10914348785264469</v>
@@ -22246,7 +22229,7 @@
     </row>
     <row r="68" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A68" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B68">
         <v>0.1134134012280789</v>
@@ -22536,7 +22519,7 @@
     </row>
     <row r="69" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A69" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B69">
         <v>-1.9289311962133571E-2</v>
@@ -23116,7 +23099,7 @@
     </row>
     <row r="71" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A71" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="B71">
         <v>0.37654161757349719</v>
@@ -24566,7 +24549,7 @@
     </row>
     <row r="76" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A76" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="B76">
         <v>-6.6538694525457742E-2</v>
@@ -25726,7 +25709,7 @@
     </row>
     <row r="80" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A80" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B80">
         <v>0.19570579834879587</v>
@@ -26016,7 +25999,7 @@
     </row>
     <row r="81" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A81" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B81">
         <v>0.26175798949486129</v>
@@ -28046,7 +28029,7 @@
     </row>
     <row r="88" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A88" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B88">
         <v>6.1450097980914692E-2</v>
@@ -28336,7 +28319,7 @@
     </row>
     <row r="89" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A89" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B89">
         <v>5.3925115691330648E-2</v>
@@ -28626,7 +28609,7 @@
     </row>
     <row r="90" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A90" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B90">
         <v>0.14578528428331583</v>
@@ -28916,7 +28899,7 @@
     </row>
     <row r="91" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A91" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B91">
         <v>-0.15868877718589428</v>
@@ -29206,7 +29189,7 @@
     </row>
     <row r="92" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A92" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B92">
         <v>9.4505998910818009E-3</v>
@@ -29786,7 +29769,7 @@
     </row>
     <row r="94" spans="1:96" x14ac:dyDescent="0.45">
       <c r="A94" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B94">
         <v>0.49327501480259495</v>
@@ -30448,16 +30431,16 @@
         <v>25</v>
       </c>
       <c r="X1" t="s">
+        <v>144</v>
+      </c>
+      <c r="Y1" t="s">
         <v>145</v>
       </c>
-      <c r="Y1" t="s">
+      <c r="Z1" t="s">
         <v>146</v>
       </c>
-      <c r="Z1" t="s">
+      <c r="AA1" t="s">
         <v>147</v>
-      </c>
-      <c r="AA1" t="s">
-        <v>148</v>
       </c>
       <c r="AB1" t="s">
         <v>15</v>
@@ -32469,7 +32452,7 @@
     </row>
     <row r="23" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A23" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="B23">
         <v>0.13170525734625679</v>
@@ -32564,7 +32547,7 @@
     </row>
     <row r="24" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A24" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B24">
         <v>0.11527639326460247</v>
@@ -32659,7 +32642,7 @@
     </row>
     <row r="25" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A25" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B25">
         <v>4.1451124133798289E-3</v>
@@ -32754,7 +32737,7 @@
     </row>
     <row r="26" spans="1:31" x14ac:dyDescent="0.45">
       <c r="A26" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B26">
         <v>0.10987169233135002</v>
